--- a/data/hex_xlsx/ROBIT.HE.xlsx
+++ b/data/hex_xlsx/ROBIT.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="360">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -657,70 +657,73 @@
     <t>Non-current liabilities</t>
   </si>
   <si>
+    <t>Loans from Credit Institutions LT</t>
+  </si>
+  <si>
+    <t>Other Loans</t>
+  </si>
+  <si>
+    <t>Long-Term Debt excluding Capitalized Leases - Balancing value</t>
+  </si>
+  <si>
+    <t>Lease liabilities</t>
+  </si>
+  <si>
+    <t>Deferred tax liabilities</t>
+  </si>
+  <si>
+    <t>Derivative Liabilities - Hedging - Long-Term</t>
+  </si>
+  <si>
+    <t>Employee benefit obligations</t>
+  </si>
+  <si>
+    <t>Balancing Item - Noncurrent Liabilities</t>
+  </si>
+  <si>
+    <t>Total non-current liabilities</t>
+  </si>
+  <si>
+    <t>Income tax liabilities</t>
+  </si>
+  <si>
+    <t>Account payables and other liabilities</t>
+  </si>
+  <si>
+    <t>Accounts Payable</t>
+  </si>
+  <si>
+    <t>Accrued interests</t>
+  </si>
+  <si>
+    <t>Accrued salaries</t>
+  </si>
+  <si>
+    <t>Accrued Expenses - Balancing value</t>
+  </si>
+  <si>
+    <t>Other Payables</t>
+  </si>
+  <si>
+    <t>Account payables and other liabilities - Balancing value</t>
+  </si>
+  <si>
+    <t>Advances received</t>
+  </si>
+  <si>
+    <t>Short-Term Debt &amp; Current Portion of Long-Term Debt</t>
+  </si>
+  <si>
+    <t>Short-Term Debt &amp; Current Portion of Long-Term Debt - Balancing value</t>
+  </si>
+  <si>
+    <t>Current liabilities</t>
+  </si>
+  <si>
+    <t>Bank Overdrafts</t>
+  </si>
+  <si>
     <t>Loans from Credit Institutions</t>
-  </si>
-  <si>
-    <t>Other Loans</t>
-  </si>
-  <si>
-    <t>Long-Term Debt excluding Capitalized Leases - Balancing value</t>
-  </si>
-  <si>
-    <t>Lease liabilities</t>
-  </si>
-  <si>
-    <t>Deferred tax liabilities</t>
-  </si>
-  <si>
-    <t>Derivative Liabilities - Hedging - Long-Term</t>
-  </si>
-  <si>
-    <t>Employee benefit obligations</t>
-  </si>
-  <si>
-    <t>Balancing Item - Noncurrent Liabilities</t>
-  </si>
-  <si>
-    <t>Total non-current liabilities</t>
-  </si>
-  <si>
-    <t>Income tax liabilities</t>
-  </si>
-  <si>
-    <t>Account payables and other liabilities</t>
-  </si>
-  <si>
-    <t>Accounts Payable</t>
-  </si>
-  <si>
-    <t>Accrued interests</t>
-  </si>
-  <si>
-    <t>Accrued salaries</t>
-  </si>
-  <si>
-    <t>Accrued Expenses - Balancing value</t>
-  </si>
-  <si>
-    <t>Other Payables</t>
-  </si>
-  <si>
-    <t>Account payables and other liabilities - Balancing value</t>
-  </si>
-  <si>
-    <t>Advances received</t>
-  </si>
-  <si>
-    <t>Short-Term Debt &amp; Current Portion of Long-Term Debt</t>
-  </si>
-  <si>
-    <t>Short-Term Debt &amp; Current Portion of Long-Term Debt - Balancing value</t>
-  </si>
-  <si>
-    <t>Current liabilities</t>
-  </si>
-  <si>
-    <t>Bank Overdrafts</t>
   </si>
   <si>
     <t>Current Portion of Long-Term Debt excluding Capitalized Leases - Balancing value</t>
@@ -1221,7 +1224,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1299,6 +1302,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -7840,7 +7846,7 @@
       <c r="K78" s="18"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="26" t="s">
         <v>212</v>
       </c>
       <c r="B79" s="18"/>
@@ -8505,7 +8511,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="B103" s="18"/>
       <c r="C103" s="20">
@@ -8538,7 +8544,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B104" s="18"/>
       <c r="C104" s="18"/>
@@ -8555,7 +8561,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B105" s="20">
         <v>0.39</v>
@@ -8586,7 +8592,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B106" s="18"/>
       <c r="C106" s="18"/>
@@ -8605,7 +8611,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B107" s="17">
         <v>257.81</v>
@@ -8640,7 +8646,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -8659,7 +8665,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B109" s="17">
         <v>471.76</v>
@@ -8694,7 +8700,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B110" s="18"/>
       <c r="C110" s="18"/>
@@ -8711,7 +8717,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B111" s="17">
         <v>979.9</v>
@@ -8746,7 +8752,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B112" s="18"/>
       <c r="C112" s="20">
@@ -8779,7 +8785,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B113" s="18"/>
       <c r="C113" s="20">
@@ -8812,7 +8818,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B114" s="18"/>
       <c r="C114" s="20">
@@ -8845,7 +8851,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B115" s="18"/>
       <c r="C115" s="20">
@@ -8876,7 +8882,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="20">
@@ -8907,7 +8913,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B117" s="18"/>
       <c r="C117" s="20">
@@ -8934,7 +8940,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B118" s="18"/>
       <c r="C118" s="20">
@@ -8965,7 +8971,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B119" s="18"/>
       <c r="C119" s="20">
@@ -8996,7 +9002,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B120" s="18"/>
       <c r="C120" s="19">
@@ -9019,7 +9025,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B121" s="18"/>
       <c r="C121" s="20">
@@ -9052,7 +9058,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B122" s="18"/>
       <c r="C122" s="20">
@@ -9085,7 +9091,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B123" s="18"/>
       <c r="C123" s="20">
@@ -9118,7 +9124,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B124" s="18"/>
       <c r="C124" s="20">
@@ -10047,7 +10053,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10264,31 +10270,31 @@
         <v>32</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -10325,7 +10331,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -10371,7 +10377,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B20" s="20">
         <v>1.04</v>
@@ -10403,7 +10409,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -10421,7 +10427,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B22" s="20">
         <v>44.18</v>
@@ -10449,7 +10455,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" s="20">
         <v>15.28</v>
@@ -10481,7 +10487,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B24" s="20">
         <v>0.97</v>
@@ -10513,7 +10519,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="20">
@@ -10543,7 +10549,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -10559,7 +10565,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" s="20">
         <v>8.17</v>
@@ -10591,7 +10597,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B28" s="20">
         <v>17.38</v>
@@ -10623,7 +10629,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B29" s="20">
         <v>0.35</v>
@@ -10655,7 +10661,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B30" s="19">
         <v>-2.98</v>
@@ -10687,7 +10693,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B31" s="19">
         <v>-12.91</v>
@@ -10719,7 +10725,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B32" s="20">
         <v>1.43</v>
@@ -10751,7 +10757,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" s="19">
         <v>-3.94</v>
@@ -10783,7 +10789,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -10805,7 +10811,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B35" s="22">
         <v>69.29</v>
@@ -10837,7 +10843,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B36" s="19">
         <v>-11.25</v>
@@ -10869,7 +10875,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="20">
@@ -10887,7 +10893,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B38" s="19">
         <v>-0.88</v>
@@ -10919,7 +10925,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="20">
@@ -10949,7 +10955,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B40" s="20">
         <v>0.77</v>
@@ -10981,7 +10987,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -10999,7 +11005,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="19">
@@ -11019,7 +11025,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B43" s="23">
         <v>-11.68</v>
@@ -11051,7 +11057,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -11073,7 +11079,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
@@ -11091,7 +11097,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="19">
@@ -11109,7 +11115,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18">
@@ -11133,7 +11139,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B48" s="25">
         <v>-257.36</v>
@@ -11163,7 +11169,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B49" s="19">
         <v>-1.23</v>
@@ -11195,7 +11201,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B50" s="19">
         <v>-17.93</v>
@@ -11227,7 +11233,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B51" s="19">
         <v>-0.3</v>
@@ -11251,7 +11257,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -11269,7 +11275,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
@@ -11289,7 +11295,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B54" s="15">
         <v>228.2</v>
@@ -11305,7 +11311,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B55" s="23">
         <v>-48.62</v>
@@ -11337,7 +11343,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B56" s="15">
         <v>106.8</v>
@@ -11369,7 +11375,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B57" s="15">
         <v>112.41</v>
@@ -11401,7 +11407,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B58" s="19">
         <v>-3.43</v>
@@ -11433,7 +11439,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B59" s="20">
         <v>8.99</v>
@@ -11465,7 +11471,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="23">
@@ -12455,7 +12461,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12573,22 +12579,22 @@
         <v>26</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -12828,7 +12834,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -12874,1446 +12880,1446 @@
         <v>45</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K19" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" s="30">
         <v>547.1</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>581.73</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>876.17</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>1161.95</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>1015.83</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>819.31</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>494.46</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>1400.6</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>1460.05</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>644.54</v>
       </c>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" s="30">
         <v>929.83</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>966.09</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>901.15</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>978.03</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>1117.16</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <v>990.68</v>
       </c>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="B24" s="30">
         <v>323.99</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>357.72</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>572.17</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>838.8</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>794.97</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>593.3</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>337.81</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="30">
         <v>1324.28</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>1123.52</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>854.05</v>
       </c>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="B25" s="30">
         <v>644.26</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>685.67</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>647.15</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>778.02</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>897.84</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <v>869.11</v>
       </c>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" s="32">
         <v>15.3</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>16.89</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>27.14</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>39.78</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>37.71</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>28.14</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>16.02</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>62.81</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>70.73</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>53.77</v>
       </c>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="A28" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="B28" s="32">
         <v>30.53</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>32.51</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>30.69</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>36.9</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>46.61</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>47.72</v>
       </c>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
+      <c r="A29" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="A30" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="B30" s="33">
         <v>3.81</v>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="33">
         <v>24.78</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="33">
         <v>7.84</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>-10.12</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <v>3.95</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>-1.56</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>-20.16</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>-11.15</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>-2.49</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>-3.6</v>
       </c>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
-      <c r="O30" s="32"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="B31" s="32">
+      <c r="A31" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="B31" s="33">
         <v>2.83</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <v>1.88</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>-2.92</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>-7.28</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>-5.1</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>-6.02</v>
       </c>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
+      <c r="A32" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="A33" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B33" s="33">
         <v>0.0</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <v>0.0</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="33">
         <v>0.0</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="33">
         <v>0.0</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="33">
         <v>0.0</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <v>0.0</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="33">
         <v>6.18</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="33">
         <v>1.57</v>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="33">
         <v>0.51</v>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="33">
         <v>0.0</v>
       </c>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="B34" s="32">
+      <c r="A34" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" s="33">
         <v>0.0</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>0.0</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="33">
         <v>0.68</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="33">
         <v>1.09</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="33">
         <v>1.08</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <v>0.99</v>
       </c>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="32"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="B35" s="32">
+      <c r="A35" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="B35" s="33">
         <v>0.0</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="33">
         <v>0.0</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="33">
         <v>0.0</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="33">
         <v>0.0</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="33">
         <v>0.0</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <v>0.0</v>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="33">
         <v>6.18</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="33">
         <v>1.57</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="33">
         <v>0.51</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="33">
         <v>0.0</v>
       </c>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>324</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="B36" s="33">
         <v>0.0</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>0.0</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>0.68</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="33">
         <v>1.09</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="33">
         <v>1.08</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <v>0.99</v>
       </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="32"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>326</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" s="32">
         <v>0.6</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>0.7</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>1.08</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>1.72</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>1.61</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>1.18</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>0.59</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>1.45</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>2.36</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>1.9</v>
       </c>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="B39" s="32">
         <v>1.15</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>1.26</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>1.21</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>1.31</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>1.47</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>1.53</v>
       </c>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>329</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B41" s="32">
         <v>0.69</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>0.81</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>1.25</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>2.06</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>1.99</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>1.5</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>0.75</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>2.27</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>7.55</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="32">
         <v>1.96</v>
       </c>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B42" s="32">
         <v>1.36</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>1.52</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <v>1.48</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <v>1.74</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <v>2.29</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <v>2.25</v>
       </c>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B44" s="32">
         <v>0.3</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>0.34</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>0.49</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>0.83</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>0.82</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.69</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.41</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>1.39</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>1.94</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>1.94</v>
       </c>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="B45" s="32">
         <v>0.56</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>0.63</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>0.65</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>0.85</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>1.06</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <v>1.24</v>
       </c>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="B47" s="32">
         <v>26.23</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <v>4.03</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <v>12.75</v>
       </c>
-      <c r="E47" s="30"/>
-      <c r="F47" s="31">
+      <c r="E47" s="31"/>
+      <c r="F47" s="32">
         <v>25.33</v>
       </c>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="B48" s="31">
+      <c r="A48" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="B48" s="32">
         <v>35.38</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <v>53.33</v>
       </c>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B50" s="32">
         <v>5.39</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>17.62</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>8.19</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>13.07</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>24.44</v>
       </c>
-      <c r="G50" s="29">
+      <c r="G50" s="30">
         <v>560.35</v>
       </c>
-      <c r="H50" s="30"/>
-      <c r="I50" s="29">
+      <c r="H50" s="31"/>
+      <c r="I50" s="30">
         <v>1592.66</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="32">
         <v>12.52</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="32">
         <v>31.03</v>
       </c>
-      <c r="L50" s="30"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="30"/>
-      <c r="O50" s="30"/>
+      <c r="L50" s="31"/>
+      <c r="M50" s="31"/>
+      <c r="N50" s="31"/>
+      <c r="O50" s="31"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>339</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="B51" s="32">
         <v>11.86</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>16.94</v>
       </c>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="30"/>
-      <c r="O51" s="30"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="B53" s="31">
+      <c r="A53" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="B53" s="32">
         <v>24.99</v>
       </c>
-      <c r="C53" s="30"/>
-      <c r="D53" s="31">
+      <c r="C53" s="31"/>
+      <c r="D53" s="32">
         <v>66.66</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="32">
         <v>99.35</v>
       </c>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="30"/>
-      <c r="J53" s="31">
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="32">
         <v>26.86</v>
       </c>
-      <c r="K53" s="31">
+      <c r="K53" s="32">
         <v>51.88</v>
       </c>
-      <c r="L53" s="30"/>
-      <c r="M53" s="30"/>
-      <c r="N53" s="30"/>
-      <c r="O53" s="30"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
+      <c r="A54" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="B55" s="31">
+      <c r="A55" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B55" s="32">
         <v>24.99</v>
       </c>
-      <c r="C55" s="30"/>
-      <c r="D55" s="31">
+      <c r="C55" s="31"/>
+      <c r="D55" s="32">
         <v>66.66</v>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="32">
         <v>99.25</v>
       </c>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="31">
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="32">
         <v>26.86</v>
       </c>
-      <c r="K55" s="31">
+      <c r="K55" s="32">
         <v>51.88</v>
       </c>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>344</v>
-      </c>
-      <c r="B56" s="31">
+      <c r="A56" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="B56" s="32">
         <v>1.15</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>1.26</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>1.21</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>1.31</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>1.47</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <v>1.53</v>
       </c>
-      <c r="H56" s="30"/>
-      <c r="I56" s="30"/>
-      <c r="J56" s="30"/>
-      <c r="K56" s="30"/>
-      <c r="L56" s="30"/>
-      <c r="M56" s="30"/>
-      <c r="N56" s="30"/>
-      <c r="O56" s="30"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="31"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
+      <c r="M56" s="31"/>
+      <c r="N56" s="31"/>
+      <c r="O56" s="31"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
+      <c r="A57" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>346</v>
-      </c>
-      <c r="B58" s="31">
+      <c r="A58" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="B58" s="32">
         <v>0.18</v>
       </c>
-      <c r="C58" s="30"/>
-      <c r="D58" s="34">
+      <c r="C58" s="31"/>
+      <c r="D58" s="35">
         <v>-22.79</v>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="32">
         <v>0.77</v>
       </c>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="31">
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="32">
         <v>0.16</v>
       </c>
-      <c r="K58" s="34">
+      <c r="K58" s="35">
         <v>-0.83</v>
       </c>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27"/>
-      <c r="O59" s="27"/>
+      <c r="A59" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="28"/>
+      <c r="O59" s="28"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>348</v>
-      </c>
-      <c r="B60" s="31">
+      <c r="A60" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="B60" s="32">
         <v>0.51</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="32">
         <v>0.56</v>
       </c>
-      <c r="D60" s="31">
+      <c r="D60" s="32">
         <v>0.75</v>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="32">
         <v>1.15</v>
       </c>
-      <c r="F60" s="31">
+      <c r="F60" s="32">
         <v>1.06</v>
       </c>
-      <c r="G60" s="31">
+      <c r="G60" s="32">
         <v>0.96</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="32">
         <v>0.6</v>
       </c>
-      <c r="I60" s="31">
+      <c r="I60" s="32">
         <v>1.61</v>
       </c>
-      <c r="J60" s="31">
+      <c r="J60" s="32">
         <v>2.52</v>
       </c>
-      <c r="K60" s="31">
+      <c r="K60" s="32">
         <v>1.47</v>
       </c>
-      <c r="L60" s="30"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="30"/>
-      <c r="O60" s="30"/>
+      <c r="L60" s="31"/>
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="B61" s="31">
+      <c r="A61" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="B61" s="32">
         <v>0.81</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="32">
         <v>0.89</v>
       </c>
-      <c r="D61" s="31">
+      <c r="D61" s="32">
         <v>0.91</v>
       </c>
-      <c r="E61" s="31">
+      <c r="E61" s="32">
         <v>1.09</v>
       </c>
-      <c r="F61" s="31">
+      <c r="F61" s="32">
         <v>1.29</v>
       </c>
-      <c r="G61" s="31">
+      <c r="G61" s="32">
         <v>1.37</v>
       </c>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="27"/>
-      <c r="K62" s="27"/>
-      <c r="L62" s="27"/>
-      <c r="M62" s="27"/>
-      <c r="N62" s="27"/>
-      <c r="O62" s="27"/>
+      <c r="A62" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="28"/>
+      <c r="K62" s="28"/>
+      <c r="L62" s="28"/>
+      <c r="M62" s="28"/>
+      <c r="N62" s="28"/>
+      <c r="O62" s="28"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>351</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="B63" s="32">
         <v>8.39</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>10.22</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>6.44</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>13.04</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>12.0</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <v>31.72</v>
       </c>
-      <c r="H63" s="30"/>
-      <c r="I63" s="31">
+      <c r="H63" s="31"/>
+      <c r="I63" s="32">
         <v>87.44</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="32">
         <v>15.57</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="32">
         <v>17.2</v>
       </c>
-      <c r="L63" s="30"/>
-      <c r="M63" s="30"/>
-      <c r="N63" s="30"/>
-      <c r="O63" s="30"/>
+      <c r="L63" s="31"/>
+      <c r="M63" s="31"/>
+      <c r="N63" s="31"/>
+      <c r="O63" s="31"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>352</v>
-      </c>
-      <c r="B64" s="31">
+      <c r="A64" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="B64" s="32">
         <v>9.74</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="32">
         <v>11.47</v>
       </c>
-      <c r="D64" s="31">
+      <c r="D64" s="32">
         <v>50.52</v>
       </c>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="26" t="s">
-        <v>353</v>
-      </c>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-      <c r="J65" s="27"/>
-      <c r="K65" s="27"/>
-      <c r="L65" s="27"/>
-      <c r="M65" s="27"/>
-      <c r="N65" s="27"/>
-      <c r="O65" s="27"/>
+      <c r="A65" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28"/>
+      <c r="J65" s="28"/>
+      <c r="K65" s="28"/>
+      <c r="L65" s="28"/>
+      <c r="M65" s="28"/>
+      <c r="N65" s="28"/>
+      <c r="O65" s="28"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="B66" s="32">
         <v>30.65</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>6.23</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>14.91</v>
       </c>
-      <c r="E66" s="30"/>
-      <c r="F66" s="31">
+      <c r="E66" s="31"/>
+      <c r="F66" s="32">
         <v>22.75</v>
       </c>
-      <c r="G66" s="29">
+      <c r="G66" s="30">
         <v>189.65</v>
       </c>
-      <c r="H66" s="30"/>
-      <c r="I66" s="30"/>
-      <c r="J66" s="29">
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="30">
         <v>615.12</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="32">
         <v>25.6</v>
       </c>
-      <c r="L66" s="30"/>
-      <c r="M66" s="30"/>
-      <c r="N66" s="30"/>
-      <c r="O66" s="30"/>
+      <c r="L66" s="31"/>
+      <c r="M66" s="31"/>
+      <c r="N66" s="31"/>
+      <c r="O66" s="31"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="B67" s="31">
+      <c r="A67" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="B67" s="32">
         <v>25.38</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="32">
         <v>29.81</v>
       </c>
-      <c r="D67" s="29">
+      <c r="D67" s="30">
         <v>109.52</v>
       </c>
-      <c r="E67" s="30"/>
-      <c r="F67" s="29">
+      <c r="E67" s="31"/>
+      <c r="F67" s="30">
         <v>736.48</v>
       </c>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="26" t="s">
-        <v>356</v>
-      </c>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="27"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
-      <c r="J68" s="27"/>
-      <c r="K68" s="27"/>
-      <c r="L68" s="27"/>
-      <c r="M68" s="27"/>
-      <c r="N68" s="27"/>
-      <c r="O68" s="27"/>
+      <c r="A68" s="27" t="s">
+        <v>357</v>
+      </c>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="28"/>
+      <c r="K68" s="28"/>
+      <c r="L68" s="28"/>
+      <c r="M68" s="28"/>
+      <c r="N68" s="28"/>
+      <c r="O68" s="28"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="B69" s="32">
         <v>44.41</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>6.58</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>19.52</v>
       </c>
-      <c r="E69" s="30"/>
-      <c r="F69" s="31">
+      <c r="E69" s="31"/>
+      <c r="F69" s="32">
         <v>32.52</v>
       </c>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="30"/>
-      <c r="K69" s="30"/>
-      <c r="L69" s="30"/>
-      <c r="M69" s="30"/>
-      <c r="N69" s="30"/>
-      <c r="O69" s="30"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
+      <c r="N69" s="31"/>
+      <c r="O69" s="31"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>358</v>
-      </c>
-      <c r="B70" s="31">
+      <c r="A70" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="B70" s="32">
         <v>50.96</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="32">
         <v>74.85</v>
       </c>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
-      <c r="O70" s="30"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
     <row r="72" ht="15.75" customHeight="1"/>
